--- a/Assets/ExcelImporter/ShipData/ShipData_SO.xlsx
+++ b/Assets/ExcelImporter/ShipData/ShipData_SO.xlsx
@@ -123,37 +123,10 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1B1C1D"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1B1C1D"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -497,27 +470,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFDEE0E3"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFDEE0E3"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFDEE0E3"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -638,153 +596,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1312,165 +1258,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5"/>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="10.5769230769231" customWidth="1"/>
-    <col min="3" max="4" width="10.4134615384615" customWidth="1"/>
-    <col min="5" max="6" width="17.3076923076923" customWidth="1"/>
-    <col min="7" max="7" width="118.586538461538" customWidth="1"/>
-    <col min="8" max="8" width="12.6538461538462" customWidth="1"/>
-    <col min="9" max="9" width="100.788461538462" customWidth="1"/>
+    <col min="1" max="1" width="9.23076923076923" style="1"/>
+    <col min="2" max="2" width="10.5769230769231" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.4134615384615" style="1" customWidth="1"/>
+    <col min="5" max="6" width="17.3076923076923" style="1" customWidth="1"/>
+    <col min="7" max="7" width="230.923076923077" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.3365384615385" style="1" customWidth="1"/>
+    <col min="9" max="9" width="184.615384615385" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.23076923076923" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="17" spans="1:9">
-      <c r="A2">
+    <row r="2" spans="1:9">
+      <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="1">
         <v>1</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="17" spans="1:9">
-      <c r="A3">
+    <row r="3" spans="1:9">
+      <c r="A3" s="1">
         <v>14</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>0</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>1</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>16</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>1</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>28</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>0</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>1</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="5:6">
-      <c r="E6" s="5"/>
-      <c r="F6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/ExcelImporter/ShipData/ShipData_SO.xlsx
+++ b/Assets/ExcelImporter/ShipData/ShipData_SO.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>uid</t>
   </si>
@@ -71,6 +71,18 @@
     <t>[{"x":0,"y":1},{"x":1,"y":1},{"x":0,"y":0},{"x":1,"y":0}]</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>interference</t>
+  </si>
+  <si>
+    <t>频谱干扰艇</t>
+  </si>
+  <si>
+    <t>[{"x":0,"y":0},{"x":0,"y":1},{"x":-1,"y":0},{"x":1,"y":0},{"x":-1,"y":-1},{"x":0,"y":-1},{"x":1,"y":-1}]</t>
+  </si>
+  <si>
     <t>bomb_focus</t>
   </si>
   <si>
@@ -81,9 +93,6 @@
   </si>
   <si>
     <t>[{"x":0,"y":0},{"x":1,"y":0}]</t>
-  </si>
-  <si>
-    <t>B</t>
   </si>
   <si>
     <t>bomb_wide</t>
@@ -1258,8 +1267,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="9.23076923076923" style="1"/>
     <col min="2" max="2" width="10.5769230769231" style="1" customWidth="1"/>
@@ -1329,91 +1338,120 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" s="1" customFormat="1" spans="1:9">
       <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="1">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>27</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/ExcelImporter/ShipData/ShipData_SO.xlsx
+++ b/Assets/ExcelImporter/ShipData/ShipData_SO.xlsx
@@ -119,7 +119,7 @@
     <t>[{"x":0,"y":0},{"x":0,"y":1},{"x":-1,"y":0}]</t>
   </si>
   <si>
-    <t>[{"x":0,"y":0},{"x":0,"y":1}]</t>
+    <t>[{"x":0,"y":0}]</t>
   </si>
 </sst>
 </file>
